--- a/blog/posts/germany-persons-seeking-protection-stacked-area-chart/persons-seeking-protection-germany.xlsx
+++ b/blog/posts/germany-persons-seeking-protection-stacked-area-chart/persons-seeking-protection-germany.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unitednations-my.sharepoint.com/personal/juan_torresmunguia_un_org/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jator\Documents\GitHub\personal_page\juan-torresmunguia_Quarto\blog\posts\germany-persons-seeking-protection-stacked-area-chart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{492AEB5A-5416-41C9-8CA9-0F226E9F880C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39D88BE-49FE-4646-8531-6BFB4DACE09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0814471A-4C3D-47D2-98EF-06277C00EA2A}"/>
+    <workbookView xWindow="5856" yWindow="24" windowWidth="17280" windowHeight="8880" xr2:uid="{0814471A-4C3D-47D2-98EF-06277C00EA2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -503,7 +503,7 @@
   <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="17.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
